--- a/output/2026-09-08_21_Croazia_Sisacko-moslavacka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-08_21_Croazia_Sisacko-moslavacka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,6 @@
           <t>A.B.S. Alati d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Kutina, Sisačko-moslavačka županija</t>
@@ -574,7 +573,6 @@
           <t>+385 51 372 154 / +385 51 372 029</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Ingrosso di utensili manuali (trgovina na veliko alatima), attività confermata dal 2010. Micro-impresa (1 dipendente). Nessun sito web ufficiale reperito, email non verificabile. Verificato tramite ricerca web (fininfo.hr, insolve.hr).</t>
@@ -582,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -624,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
